--- a/output/full_scan/batch_seq6_2026-10-19.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-19.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6418</v>
+        <v>6277</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>979.7738106319232</v>
+        <v>1189</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>40</v>
+        <v>88.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>74.26574326128211</v>
+        <v>79.36047406397756</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>27.31958886955651</v>
+        <v>29.19820269168374</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.031292432873931</v>
+        <v>5.952885844864476</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3478782737288544</v>
+        <v>1.127982228551314</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6233</v>
+        <v>6418</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>905.079255333943</v>
+        <v>1179.773810631923</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>26.5</v>
+        <v>40</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>83.8755310557967</v>
+        <v>74.26574338459881</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46.35665157387449</v>
+        <v>27.31958891982406</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.107925533394304</v>
+        <v>3.031292432873931</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2520445534565646</v>
+        <v>0.3478782735606142</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6245</v>
+        <v>6233</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>865.3380020307221</v>
+        <v>1105.079255333943</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>26.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>59.93774281117807</v>
+        <v>83.87553107879401</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.11947637784726</v>
+        <v>46.35665159409218</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.7523133239531979</v>
+        <v>3.107925533394304</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0229785340627406</v>
+        <v>0.252044553444543</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6209</v>
+        <v>6245</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>815.9100770103968</v>
+        <v>1035.338002030722</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>102</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>77.10552435318705</v>
+        <v>59.93774271495536</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45.40946466142225</v>
+        <v>33.11947645216795</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.691007701039675</v>
+        <v>0.7523133239531979</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.450493963149396</v>
+        <v>0.0229785353606124</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6234</v>
+        <v>6209</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>806.2451373637757</v>
+        <v>1015.910077010397</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>48.8</v>
+        <v>102</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>69.62889605476052</v>
+        <v>77.1055243413858</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>28.84100436555082</v>
+        <v>45.40946457802121</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.224513736377567</v>
+        <v>2.691007701039675</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.8868118622162631</v>
+        <v>1.450493963521935</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6277</v>
+        <v>6234</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>804</v>
+        <v>1006.245137363776</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>88.8</v>
+        <v>48.8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>79.36047405722329</v>
+        <v>69.62889608242764</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29.19820267827866</v>
+        <v>28.84100439387989</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5.952885844864476</v>
+        <v>4.224513736377567</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.127982228551314</v>
+        <v>0.8868118621201253</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6465</v>
+        <v>6278</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>724</v>
+        <v>982.383259154117</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>47.45</v>
+        <v>289.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>70.81930733969929</v>
+        <v>73.5076861918713</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15.77651223070187</v>
+        <v>49.36274694858344</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.88525743951939</v>
+        <v>1.034864684458224</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.7649917830482987</v>
+        <v>6.598037871509124</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6416</v>
+        <v>6214</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>700.7303406670085</v>
+        <v>956.247561848382</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>121</v>
+        <v>196.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>58.84247294726684</v>
+        <v>72.32283666192342</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>35.44005120144211</v>
+        <v>29.1856209846781</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5099229432690147</v>
+        <v>0.6061451752412688</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.4743832168207613</v>
+        <v>-0.0195712507823992</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6196</v>
+        <v>6465</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>694.8565225205634</v>
+        <v>924</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>598</v>
+        <v>47.45</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>51.41203799120535</v>
+        <v>70.81930739180605</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>35.76360301148439</v>
+        <v>15.77651225558491</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.4582408255353581</v>
+        <v>10.88525743951939</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-5.215807759735185</v>
+        <v>0.7649917829865137</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6271</v>
+        <v>6226</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>678.738519892271</v>
+        <v>912.0659869570422</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>225.5</v>
+        <v>41.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45.79942543830407</v>
+        <v>53.49333399488923</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.81044108366084</v>
+        <v>41.57263454409883</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6220612504703914</v>
+        <v>0.678736154126876</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-1.973473670217745</v>
+        <v>-1.064430400288682</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6226</v>
+        <v>6416</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>677.0659869570422</v>
+        <v>870.7303406670085</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>41.7</v>
+        <v>121</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>53.49333398508336</v>
+        <v>58.84247289281399</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>41.57263452175947</v>
+        <v>35.44005120146647</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.678736154126876</v>
+        <v>0.5099229432690147</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-1.064430400247821</v>
+        <v>-0.4743832161718204</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6207</v>
+        <v>6165</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>675.4118320421926</v>
+        <v>816.8013637511408</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>132</v>
+        <v>50.1</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>51.79481088533132</v>
+        <v>58.51743305908967</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.57386152329692</v>
+        <v>12.63479781907927</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.3770293628988927</v>
+        <v>0.9928800208273124</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.883749580827265</v>
+        <v>0.0598675605976376</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6214</v>
+        <v>6196</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>671.2475618483821</v>
+        <v>809.8565225205635</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>196.5</v>
+        <v>598</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>72.32283664831678</v>
+        <v>51.41203801478665</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29.1856209846781</v>
+        <v>35.76360289108164</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6061451752412688</v>
+        <v>0.4582408255353581</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.0195712510227248</v>
+        <v>-5.21580775757208</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6438</v>
+        <v>6191</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>658.7803500292821</v>
+        <v>798.8777283850605</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>54.49605173465695</v>
+        <v>58.30466487263692</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>39.14246725134636</v>
+        <v>29.65414567250781</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.739601273242506</v>
+        <v>1.378756681309978</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.3121632554298408</v>
+        <v>0.6527741717681137</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6173</v>
+        <v>6207</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>637.7177630882898</v>
+        <v>790.4118320421926</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>271.5</v>
+        <v>132</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>47.04138862186829</v>
+        <v>51.79481089295669</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>36.77071145186184</v>
+        <v>28.57386147570348</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.0789830391519802</v>
+        <v>0.3770293628988927</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-6.086773249353016</v>
+        <v>-1.883749579457306</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6263</v>
+        <v>6218</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>633.9677522224162</v>
+        <v>785.1352275172723</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>167.5</v>
+        <v>53.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>50.81736315437934</v>
+        <v>48.82040429002629</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>29.72037715820708</v>
+        <v>29.28536554267397</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6017525306240112</v>
+        <v>0.5666764533366938</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2180064637208412</v>
+        <v>-1.63041906533235</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6292</v>
+        <v>6438</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>633.2370920848437</v>
+        <v>783.7803500292823</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>65.5</v>
+        <v>167</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46.7459108458923</v>
+        <v>54.49605160796787</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31.04070160309786</v>
+        <v>39.14246742723103</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4535021595898674</v>
+        <v>0.739601273242506</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>2</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.535226335623042</v>
+        <v>0.3121632565113792</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6182</v>
+        <v>6446</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>629.106130847209</v>
+        <v>771.2915503890093</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>107.5</v>
+        <v>1175</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,29 +1453,29 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>41.11659683450383</v>
+        <v>44.4593536827733</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>20.77776757402956</v>
+        <v>12.90221927262644</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.2891746983013471</v>
+        <v>1.002506180972912</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-2.641237050684185</v>
+        <v>8.220837343578623</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>621.1594842900543</v>
+        <v>761.1594842900545</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>111</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>58.49341159256837</v>
+        <v>58.49341157630349</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.38518465447891</v>
+        <v>29.38518464703833</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.6580207282751424</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.3764560311202523</v>
+        <v>-0.3764560309519833</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6274</v>
+        <v>6194</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>615.9634789334087</v>
+        <v>750.451338974536</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1630</v>
+        <v>32.4</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>54.40080977209324</v>
+        <v>68.25895712689908</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.46816943674883</v>
+        <v>37.01671109768345</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.963462801125806</v>
+        <v>1.18126524881462</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-3.843520187493304</v>
+        <v>0.1738741904321723</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6197</v>
+        <v>6263</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>615.152908765239</v>
+        <v>748.9677522224163</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>333.5</v>
+        <v>167.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>48.13284258058588</v>
+        <v>50.81736315437934</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.41915431447197</v>
+        <v>29.72037717745164</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.931755060164892</v>
+        <v>0.6017525306240112</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.627732840862546</v>
+        <v>0.2180064638410161</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6218</v>
+        <v>6426</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>615.1352275172721</v>
+        <v>732.8504508864748</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>53.3</v>
+        <v>328</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>48.8204042836564</v>
+        <v>50.37374861830656</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.28536550731912</v>
+        <v>26.28586900126773</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5666764533366938</v>
+        <v>0.3265700182021752</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-1.630419065356383</v>
+        <v>-7.649527922346426</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6187</v>
+        <v>6415</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>612.5661905999086</v>
+        <v>720.4539657334622</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1405</v>
+        <v>475.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.44699116560247</v>
+        <v>59.25019772203553</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28.00495610994612</v>
+        <v>19.41130193494921</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9013061352751284</v>
+        <v>1.763387671663237</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-5.714234476312811</v>
+        <v>6.122193372288487</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6285</v>
+        <v>6470</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>597.16763379593</v>
+        <v>700.3555010692988</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>246.5</v>
+        <v>45.95</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>51.60768142988031</v>
+        <v>71.71806861719855</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21.66245307086853</v>
+        <v>31.44359179001554</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.208342017727199</v>
+        <v>0.9479558819639756</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.5133974466827813</v>
+        <v>0.3303208859789165</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6257</v>
+        <v>6271</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>591.7835369161589</v>
+        <v>698.738519892271</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>247</v>
+        <v>225.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>48.34937926173534</v>
+        <v>45.79942543830407</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.65394334057793</v>
+        <v>24.81044108865089</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.509640868082241</v>
+        <v>0.6220612504703914</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-3.194162181889951</v>
+        <v>-1.973473669616867</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6194</v>
+        <v>6269</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>580.4513389745324</v>
+        <v>684</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>32.4</v>
+        <v>80.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>68.25895695427509</v>
+        <v>70.79942218952222</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.01671110566957</v>
+        <v>19.39868732121406</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.18126524881462</v>
+        <v>12.66983451855707</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1738741905042766</v>
+        <v>1.814083358225541</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6278</v>
+        <v>6213</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>577.3832591541169</v>
+        <v>679.2661726828837</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>289.5</v>
+        <v>767</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>73.50768617210328</v>
+        <v>64.18198608012926</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>49.36274693920636</v>
+        <v>34.05225879808489</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.034864684458224</v>
+        <v>0.2819571263832052</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>6.598037871749511</v>
+        <v>2.208165329722917</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6165</v>
+        <v>6173</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>566.8013637511405</v>
+        <v>637.7177630882898</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>50.1</v>
+        <v>271.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>58.51743290053863</v>
+        <v>47.04138862744453</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>12.6347977891208</v>
+        <v>36.77071160872154</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.9928800208273124</v>
+        <v>0.0789830391519802</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0598675608860494</v>
+        <v>-6.086773249538403</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6290</v>
+        <v>6292</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>545.6482597759534</v>
+        <v>633.2370920848437</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>259.5</v>
+        <v>65.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45.01530820892799</v>
+        <v>46.74591086251454</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26.51152417182598</v>
+        <v>31.040701618884</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.992155201530743</v>
+        <v>0.4535021595898674</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-3.092806675767464</v>
+        <v>-0.5352263356711149</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6227</v>
+        <v>6236</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>544.7512082188047</v>
+        <v>629.9436944902335</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>124</v>
+        <v>17.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.22347692243331</v>
+        <v>55.98900254672812</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30.74771036630452</v>
+        <v>14.76212869197176</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2637301647482039</v>
+        <v>0.3360617555067545</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-2.079846634040085</v>
+        <v>-0.0059319659511087</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6191</v>
+        <v>6182</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>543.8777283850608</v>
+        <v>629.106130847209</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>91</v>
+        <v>107.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.30466454384158</v>
+        <v>41.11659683213151</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>29.65414558914601</v>
+        <v>20.77776763419919</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.378756681309978</v>
+        <v>0.2891746983013471</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.6527741717681137</v>
+        <v>-2.641237050612078</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6456</v>
+        <v>6409</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>540.0250571647134</v>
+        <v>622.490428631526</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>894</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>49.98150069185681</v>
+        <v>47.55866590470134</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>35.92863935369231</v>
+        <v>13.39504023040023</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5266548787479433</v>
+        <v>1.839393094370644</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.328930918383114</v>
+        <v>5.627085597723113</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6470</v>
+        <v>6225</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>530.3555010692993</v>
+        <v>621.8400364277286</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>45.95</v>
+        <v>83.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>71.7180686447449</v>
+        <v>65.61878387741261</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>31.44359171803951</v>
+        <v>30.76599843883742</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9479558819639756</v>
+        <v>0.3213025815117591</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.3303208858707689</v>
+        <v>1.737064818276718</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6426</v>
+        <v>6274</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>517.8504508864747</v>
+        <v>615.9634789334086</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>328</v>
+        <v>1630</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>50.37374862752497</v>
+        <v>54.40080981427648</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.28586898891185</v>
+        <v>20.46816947436035</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3265700182021752</v>
+        <v>0.963462801125806</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-7.649527922803081</v>
+        <v>-3.843520188695088</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6205</v>
+        <v>6197</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>517.5976615033492</v>
+        <v>615.1529087652387</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>65.8</v>
+        <v>333.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.24953568468656</v>
+        <v>48.13284257030227</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24.83243587934887</v>
+        <v>27.41915439226436</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.1973571749238801</v>
+        <v>0.931755060164892</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.823513603570921</v>
+        <v>-1.627732840502072</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6175</v>
+        <v>6187</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>508.3020262977944</v>
+        <v>612.5661905999089</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>1405</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>42.2910448761778</v>
+        <v>51.44699116503061</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.94554664628972</v>
+        <v>28.00495613916138</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4812643378645606</v>
+        <v>0.9013061352751284</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.1379227056770438</v>
+        <v>-5.714234475231478</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6190</v>
+        <v>6189</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>507.916388304682</v>
+        <v>609.3617839178214</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>68.5</v>
+        <v>48.75</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>41.93624964326136</v>
+        <v>47.0203692470191</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>22.39188857327178</v>
+        <v>22.21261115426219</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6417519828187606</v>
+        <v>1.048860380520011</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.4918680395935988</v>
+        <v>-0.0331077455031155</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6174</v>
+        <v>6449</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>507.7683419220562</v>
+        <v>604.3573984943263</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>50.3</v>
+        <v>239</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>48.75928676274668</v>
+        <v>50.34815273739344</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.59697764835301</v>
+        <v>24.1917206831789</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3306985762191293</v>
+        <v>0.5357398494326268</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.4297409330803168</v>
+        <v>1.555192903490265</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6449</v>
+        <v>6285</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>494.3573984943263</v>
+        <v>597.1676337959307</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>239</v>
+        <v>246.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.34815275502971</v>
+        <v>51.60768135940645</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24.19172064091633</v>
+        <v>21.6624532391083</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5357398494326268</v>
+        <v>1.208342017727199</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.555192901206993</v>
+        <v>0.5133974483652075</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6291</v>
+        <v>6224</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>493.3179784674261</v>
+        <v>591.7321163699618</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>398.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>35.87418701931509</v>
+        <v>38.05503589712987</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>26.28342295718212</v>
+        <v>24.43311809117548</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3121459693774498</v>
+        <v>0.4321298386993343</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>2</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-11.92572719420356</v>
+        <v>-1.317424901336897</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6168</v>
+        <v>6192</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>478.3986318935076</v>
+        <v>589.9756072620019</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>35.7</v>
+        <v>114</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45.40849891973691</v>
+        <v>54.9231226446219</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>36.91084926279409</v>
+        <v>25.6927386322627</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1917803275557232</v>
+        <v>0.8528211356215657</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.485223017857044</v>
+        <v>0.6789855306319112</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6189</v>
+        <v>6201</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>469.3617839178203</v>
+        <v>585.5419482670371</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>48.75</v>
+        <v>46.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>47.02036914404587</v>
+        <v>60.01067221555153</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>22.21261112399712</v>
+        <v>37.29512035878185</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.048860380520011</v>
+        <v>0.4045779805878448</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0331077454069769</v>
+        <v>0.239006788848847</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6244</v>
+        <v>6183</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>464.2111074337176</v>
+        <v>581.329573939285</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>21.15</v>
+        <v>89</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>37.06494183383789</v>
+        <v>32.16478854757608</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16.44763097841471</v>
+        <v>11.8234943090704</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5054904097655494</v>
+        <v>2.092534766027408</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.1829534296759463</v>
+        <v>-0.1286679275450405</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6163</v>
+        <v>6244</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>462.3154695398477</v>
+        <v>579.2111074337173</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>41.3</v>
+        <v>21.15</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45.20523794242261</v>
+        <v>37.06494190684269</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>23.51482628901233</v>
+        <v>16.44763099452359</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.7190190834704363</v>
+        <v>0.5054904097655494</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0074697373848512</v>
+        <v>-0.182953429784101</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6224</v>
+        <v>6170</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>456.7321163699618</v>
+        <v>578.7637841382102</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>49.15</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>38.05503588064393</v>
+        <v>54.68834616163154</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.43311807506494</v>
+        <v>24.39533558974522</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4321298386993343</v>
+        <v>1.412125770171743</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.317424901409004</v>
+        <v>0.0186536158082538</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6432</v>
+        <v>6163</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>454.5539635833483</v>
+        <v>577.3154695398476</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>58.1</v>
+        <v>41.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>41.71715197358756</v>
+        <v>45.20523798452154</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.36234958941581</v>
+        <v>23.51482630393041</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2496209965449199</v>
+        <v>0.7190190834704363</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.4047338819861106</v>
+        <v>0.0074697373007228</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6166</v>
+        <v>6257</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>453.4427501938629</v>
+        <v>576.7835369161589</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>106.5</v>
+        <v>247</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>31.23580513078561</v>
+        <v>48.34937928884832</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.25944336054842</v>
+        <v>34.65394336714483</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.666714090624882</v>
+        <v>0.509640868082241</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-2.443984974722304</v>
+        <v>-3.194162181938016</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6223</v>
+        <v>6414</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>451.6569141696254</v>
+        <v>561.3770537188805</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>5235</v>
+        <v>397</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.52617172860612</v>
+        <v>51.16160466278856</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.19654634257012</v>
+        <v>14.54614674847872</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9171782836705544</v>
+        <v>0.5887782896775388</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-21.5289367669986</v>
+        <v>1.256756843459876</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6451</v>
+        <v>6472</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>446.6232714914679</v>
+        <v>552.0987733042847</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>366</v>
+        <v>412.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>36.53654944001765</v>
+        <v>44.63620927176365</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.15373365215265</v>
+        <v>31.99910850136215</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6562714663257546</v>
+        <v>1.072117925031964</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-5.91964752722393</v>
+        <v>-0.6124344196775702</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6446</v>
+        <v>6290</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>441.2915503890093</v>
+        <v>545.6482597759536</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1175</v>
+        <v>259.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>44.45935371442506</v>
+        <v>45.0153082377267</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>12.90221923011312</v>
+        <v>26.51152420692849</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.002506180972912</v>
+        <v>0.992155201530743</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>8.22083734129513</v>
+        <v>-3.092806675767464</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6282</v>
+        <v>6227</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>438.9159537206038</v>
+        <v>544.7512082188047</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>42.35</v>
+        <v>124</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.52521748626042</v>
+        <v>43.22347693950822</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.97357728579904</v>
+        <v>30.74771034900002</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.026963281750843</v>
+        <v>0.2637301647482039</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0038794837270306</v>
+        <v>-2.079846633895889</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6170</v>
+        <v>6456</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>438.7637841382102</v>
+        <v>540.0250571647134</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>49.15</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.68834622457166</v>
+        <v>49.98150069758778</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.39533558974522</v>
+        <v>35.92863942632058</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.412125770171743</v>
+        <v>0.5266548787479433</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0186536157601793</v>
+        <v>-1.328930917782249</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6225</v>
+        <v>6202</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>431.8400364277286</v>
+        <v>538.1597103641435</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>83.5</v>
+        <v>55.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>65.61878389324184</v>
+        <v>42.61546078292584</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30.76599844764113</v>
+        <v>14.78822739570936</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3213025815117591</v>
+        <v>0.6717269317984238</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.737064818276718</v>
+        <v>-0.4562176295718561</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6236</v>
+        <v>6205</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>429.9436944902336</v>
+        <v>537.5976615033492</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>17.3</v>
+        <v>65.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>55.98900290353376</v>
+        <v>44.24953574096566</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.76212865173222</v>
+        <v>24.83243589164719</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3360617555067545</v>
+        <v>0.1973571749238801</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0059319660953174</v>
+        <v>-0.8235136034387285</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6202</v>
+        <v>6279</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>423.1597103641435</v>
+        <v>527.4576639585036</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>55.5</v>
+        <v>113.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>42.61546077704155</v>
+        <v>42.55770894480976</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.78822739334432</v>
+        <v>24.29744663637958</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6717269317984238</v>
+        <v>0.6944333711631799</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.4562176296679908</v>
+        <v>0.3230731341988253</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6472</v>
+        <v>6175</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>422.0987733042848</v>
+        <v>508.3020262977944</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>412.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.63620920894003</v>
+        <v>42.29104489477309</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>31.99910849034164</v>
+        <v>17.94554657010567</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.072117925031964</v>
+        <v>0.4812643378645606</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.6124344184758235</v>
+        <v>-0.1379227059173932</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6414</v>
+        <v>6190</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>421.3770537188804</v>
+        <v>507.91638830468</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>397</v>
+        <v>68.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.16160453295998</v>
+        <v>41.93624957347971</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.54614672292468</v>
+        <v>22.39188863233739</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5887782896775388</v>
+        <v>0.6417519828187606</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>1.256756844421268</v>
+        <v>-0.4918680392931569</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6192</v>
+        <v>6174</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>419.9756072620017</v>
+        <v>507.7683419220562</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>114</v>
+        <v>50.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>54.92312267300948</v>
+        <v>48.75928675381996</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>25.6927386322627</v>
+        <v>20.59697768041789</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8528211356215657</v>
+        <v>0.3306985762191293</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.6789855302713828</v>
+        <v>-0.4297409330202302</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6201</v>
+        <v>6185</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>415.541948267037</v>
+        <v>504.4822383121576</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>46.1</v>
+        <v>12.85</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>60.01067200857409</v>
+        <v>49.89137448313905</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>37.29512040130261</v>
+        <v>21.37339327339146</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4045779805878448</v>
+        <v>0.6830862974620523</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2390067889690183</v>
+        <v>0.0807579965042991</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6415</v>
+        <v>6164</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>405.4297766739535</v>
+        <v>501.8546757863308</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>475.5</v>
+        <v>12.4</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>59.25019768559677</v>
+        <v>48.33232615009571</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>19.41130190076009</v>
+        <v>31.74042327664151</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.751333613868141</v>
+        <v>0.3401901312775886</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>6.122193372889333</v>
+        <v>-0.0531819153999487</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6270</v>
+        <v>6423</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>390.4124062363131</v>
+        <v>494.7692677296559</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>28.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>38.88409944076403</v>
+        <v>48.7696497047873</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>19.11810783000262</v>
+        <v>18.66172253048649</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7534803097064863</v>
+        <v>0.5197625369278918</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1769429642795015</v>
+        <v>-0.8363084331253448</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6185</v>
+        <v>6291</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>389.4822383121576</v>
+        <v>493.3179784674261</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>12.85</v>
+        <v>398.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.89137452509074</v>
+        <v>35.87418708935387</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.37339326557576</v>
+        <v>26.28342289859036</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6830862974620523</v>
+        <v>0.3121459693774498</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.080757996480262</v>
+        <v>-11.92572719528516</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6279</v>
+        <v>6167</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>387.4576639585037</v>
+        <v>481.2519229918319</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>113.5</v>
+        <v>10.3</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>42.55770894480976</v>
+        <v>48.77258420737498</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>24.29744638260706</v>
+        <v>13.24932661199951</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6944333711631799</v>
+        <v>1.772130933703833</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.3230731338383061</v>
+        <v>0.0246709614790164</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>386.854675786331</v>
+        <v>478.3986318935076</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>12.4</v>
+        <v>35.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,49 +3891,49 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.33232612719505</v>
+        <v>45.40849892201072</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>31.74042319573466</v>
+        <v>36.91084926279409</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3401901312775886</v>
+        <v>0.1917803275557232</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0531819153638954</v>
+        <v>-1.485223017833005</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6239</v>
+        <v>6451</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>377.8115878016623</v>
+        <v>476.6232714914679</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>263</v>
+        <v>366</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>37.77596897259976</v>
+        <v>36.53654945572835</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18.12802610230828</v>
+        <v>15.15373361061027</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8561368866510723</v>
+        <v>0.6562714663257546</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-4.195251430539615</v>
+        <v>-5.91964752722393</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6265</v>
+        <v>6411</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>376.7384790293337</v>
+        <v>464.1071379504108</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>45.05</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>34.73349810922512</v>
+        <v>38.79255821632115</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>20.50861567922497</v>
+        <v>8.857961960164852</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.787214189740115</v>
+        <v>1.006007261601992</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1772420327829702</v>
+        <v>-0.2494940437531894</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6419</v>
+        <v>6161</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>374.6819652920498</v>
+        <v>460.9325723282747</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>154.5</v>
+        <v>47.35</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.61761298262711</v>
+        <v>38.99564409304981</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>18.23762890212856</v>
+        <v>8.690640416282687</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5397901472376959</v>
+        <v>0.8360144354487637</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.9279821927061636</v>
+        <v>-0.117815766563693</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6259</v>
+        <v>6266</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>369.9215419921616</v>
+        <v>455.6650422632786</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>29.9</v>
+        <v>24.9</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.84687353391552</v>
+        <v>43.44892870049115</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>17.43333982881927</v>
+        <v>14.4682582024933</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6102659552888606</v>
+        <v>0.3860007101575612</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1346461729931218</v>
+        <v>-0.123565916689202</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6269</v>
+        <v>6432</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>364</v>
+        <v>454.5539635833483</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>80.3</v>
+        <v>58.1</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>70.79942216476418</v>
+        <v>41.71715195754816</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19.39868739520013</v>
+        <v>22.36234959543238</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>12.66983451855707</v>
+        <v>0.2496209965449199</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1.814083358033246</v>
+        <v>-0.4047338819380453</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6188</v>
+        <v>6282</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>354.8892608302864</v>
+        <v>453.9159537206058</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>62</v>
+        <v>42.35</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.63083366623776</v>
+        <v>43.52521749807716</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>25.17245353317546</v>
+        <v>17.97357731295862</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.052386162345816</v>
+        <v>1.026963281750843</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.3063069486762377</v>
+        <v>-0.0038794837029954</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6423</v>
+        <v>6166</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>354.7692677296559</v>
+        <v>453.4427501938631</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>84.59999999999999</v>
+        <v>106.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,49 +4262,49 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.76964976341181</v>
+        <v>31.23580515165862</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.66172246771038</v>
+        <v>23.25944343928922</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5197625369278918</v>
+        <v>0.666714090624882</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.8363084332455089</v>
+        <v>-2.443984974530034</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6284</v>
+        <v>6223</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>346.3537487766482</v>
+        <v>451.6569141696244</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>5235</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,49 +4315,49 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>40.9355321189957</v>
+        <v>44.52617172860612</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.45544826031058</v>
+        <v>14.19654624590121</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7391525984087772</v>
+        <v>0.9171782836705544</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.3345099677585976</v>
+        <v>-21.52893675978773</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6435</v>
+        <v>6464</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>333.5066845431917</v>
+        <v>441.4315973731164</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>219</v>
+        <v>76.7</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>32.94641576311763</v>
+        <v>48.3923068864233</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.73672104506815</v>
+        <v>22.62084926684302</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5405539043684806</v>
+        <v>0.2396989997246948</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>1</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-4.0648252833949</v>
+        <v>0.0478314729326571</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6183</v>
+        <v>6176</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>331.3295739392849</v>
+        <v>440.5661711703858</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>89</v>
+        <v>91.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>32.16478838312068</v>
+        <v>51.63465816443414</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11.82349394953132</v>
+        <v>9.451097363918354</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.092534766027408</v>
+        <v>1.136473076998046</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.1286679270643492</v>
+        <v>-0.07942985208889471</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6409</v>
+        <v>6198</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>331.1617133177571</v>
+        <v>425.8663925918133</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>894</v>
+        <v>19.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.55866586933204</v>
+        <v>52.45580028743547</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.39504023111053</v>
+        <v>7.463812982583875</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.650702584628887</v>
+        <v>3.56288366624284</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>5.627085600126602</v>
+        <v>1.059611042135404</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6411</v>
+        <v>6230</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>324.1071379504108</v>
+        <v>418.6490380688023</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>110.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>38.79255781602837</v>
+        <v>46.987165628828</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>8.857961970995143</v>
+        <v>17.17086948362256</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.006007261601992</v>
+        <v>0.2712900116882318</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.2494940438973958</v>
+        <v>-0.307561550054071</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6161</v>
+        <v>6281</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>320.9325723282751</v>
+        <v>417.2305299082474</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>47.35</v>
+        <v>50.8</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>38.99564405226977</v>
+        <v>43.90851268256186</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>8.690640367782521</v>
+        <v>7.496062458620317</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8360144354487637</v>
+        <v>1.080708308810358</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1178157666478078</v>
+        <v>0.0212789724771342</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6462</v>
+        <v>6443</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>320.7960989523413</v>
+        <v>411.4982746054125</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>94.5</v>
+        <v>25.55</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.70851090197986</v>
+        <v>44.75256077975786</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.89823940900707</v>
+        <v>22.05161135900085</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.9575104814134476</v>
+        <v>0.3733764151718514</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.8839040529666432</v>
+        <v>-0.255981544784307</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6266</v>
+        <v>6217</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>315.6650422632786</v>
+        <v>406.275675195656</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>24.9</v>
+        <v>177</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>43.44892849163077</v>
+        <v>48.72468896304694</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.4682582024933</v>
+        <v>20.88049542168119</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3860007101575612</v>
+        <v>1.027567519565594</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.123565916689202</v>
+        <v>1.314804838965133</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6167</v>
+        <v>6206</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>311.251922991832</v>
+        <v>405.3657728396492</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>10.3</v>
+        <v>131.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,49 +4739,49 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.7725834193876</v>
+        <v>39.2901603679573</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.24932676518191</v>
+        <v>11.77257280465148</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.772130933703833</v>
+        <v>1.00117475381251</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0246709616202037</v>
+        <v>-0.5342051121357063</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6210</v>
+        <v>6275</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>310.1014210435184</v>
+        <v>392.7711233310262</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>18.5</v>
+        <v>44.8</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>52.80685539910306</v>
+        <v>41.28266915609157</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>5.694140828737648</v>
+        <v>24.4341880572832</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6835491309931969</v>
+        <v>0.6481770951568652</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0422826753727926</v>
+        <v>-0.2548099107128819</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6443</v>
+        <v>6270</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>296.4982746054117</v>
+        <v>390.4124062363131</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>25.55</v>
+        <v>28.2</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.75256075064285</v>
+        <v>38.88409940970509</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.05161137821477</v>
+        <v>19.11810783000263</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3733764151718514</v>
+        <v>0.7534803097064863</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.2559815447242187</v>
+        <v>-0.17694296424345</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6208</v>
+        <v>6239</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>295.7803342325959</v>
+        <v>377.8115878016623</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>263</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>35.67991469553024</v>
+        <v>37.7759689826738</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.5533572300713</v>
+        <v>18.1280261098443</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6736731365557146</v>
+        <v>0.8561368866510723</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.4409953359083629</v>
+        <v>-4.195251430539615</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6206</v>
+        <v>6265</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>290.3657728396491</v>
+        <v>376.7384790293337</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>131.5</v>
+        <v>45.05</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>39.29016026948279</v>
+        <v>34.73349808442559</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.77257277151806</v>
+        <v>20.50861568577897</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.00117475381251</v>
+        <v>0.787214189740115</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.5342051123760683</v>
+        <v>-0.1772420327108663</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6261</v>
+        <v>6419</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>289.6857104451202</v>
+        <v>374.6819652920498</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>76.3</v>
+        <v>154.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.90319673063618</v>
+        <v>48.61761299463039</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.69961172433386</v>
+        <v>18.23762906887325</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6685710445120212</v>
+        <v>0.5397901472376959</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1145481954758806</v>
+        <v>-0.9279821929465024</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6198</v>
+        <v>6259</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>285.8663925918132</v>
+        <v>369.9215419921616</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>19.5</v>
+        <v>29.9</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>52.45580028711475</v>
+        <v>45.84687353781428</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7.463813022083032</v>
+        <v>17.43333982881927</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>3.56288366624284</v>
+        <v>0.6102659552888606</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>1.059611042135404</v>
+        <v>-0.1346461729931218</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6417</v>
+        <v>6215</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>282.5603130601099</v>
+        <v>363.2330179487626</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>99.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>37.86866133799612</v>
+        <v>37.06018942262546</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25.74744843335914</v>
+        <v>15.59086507888761</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.490486142794386</v>
+        <v>0.8118968431027886</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0826093787235907</v>
+        <v>-0.5975251122694152</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6230</v>
+        <v>6177</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>278.6490380688023</v>
+        <v>358.3013994811853</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>110.5</v>
+        <v>45.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.98716551020748</v>
+        <v>39.83447788578776</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>17.17086936197201</v>
+        <v>11.91921911955102</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2712900116882318</v>
+        <v>0.9988323706350868</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.3075615501742536</v>
+        <v>-0.0310306312324886</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6281</v>
+        <v>6188</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>277.2305299082177</v>
+        <v>354.8892608302864</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>50.8</v>
+        <v>62</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.90851280976374</v>
+        <v>43.63083412412838</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7.496062456846035</v>
+        <v>25.17245353317547</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.080708308810358</v>
+        <v>1.052386162345816</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0212789724771342</v>
+        <v>0.3063069487964099</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6464</v>
+        <v>6246</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>271.4315973731163</v>
+        <v>352.3142156577222</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>76.7</v>
+        <v>12.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>48.39230699824247</v>
+        <v>44.34718263256826</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>22.62084922054475</v>
+        <v>16.8269078239959</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2396989997246948</v>
+        <v>0.6231294131608616</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.04783147283652</v>
+        <v>-0.0191272104395839</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6217</v>
+        <v>6284</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>266.2756751956559</v>
+        <v>346.3537487766482</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>177</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.72468898981666</v>
+        <v>40.93553225828664</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>20.88049563245359</v>
+        <v>15.45544833239727</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.027567519565594</v>
+        <v>0.7391525984087772</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>1.314804838039799</v>
+        <v>-0.3345099677826273</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6442</v>
+        <v>6283</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>265.0983996787769</v>
+        <v>345.9689201524328</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>1495</v>
+        <v>18.75</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>42.77247829721692</v>
+        <v>44.01576397100538</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>18.76596323801693</v>
+        <v>12.8929812879743</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5592058251376641</v>
+        <v>0.939058580070497</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-16.55025561797791</v>
+        <v>0.0362164741437052</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6275</v>
+        <v>6228</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>252.7711233310262</v>
+        <v>343.1260083368414</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>44.8</v>
+        <v>17.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.28266907496899</v>
+        <v>53.46542243693768</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>24.43418804314833</v>
+        <v>13.91986404590201</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6481770951568652</v>
+        <v>0.4379537396589566</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.254809910616741</v>
+        <v>-0.3623017907075447</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6215</v>
+        <v>6474</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>248.2330179487623</v>
+        <v>340.7527332458851</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>35.25</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.0601893075575</v>
+        <v>39.69531304494041</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.59086505712057</v>
+        <v>11.97232324464667</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8118968431027886</v>
+        <v>0.5394357523450818</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.597525112029065</v>
+        <v>0.0609257644475275</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6177</v>
+        <v>6435</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>218.3013994811853</v>
+        <v>333.5066845431917</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>45.2</v>
+        <v>219</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>39.83447791503061</v>
+        <v>32.94641577061452</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.91921910191606</v>
+        <v>16.73672112191296</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9988323706350868</v>
+        <v>0.5405539043684806</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,11 +5552,11 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0310306312685332</v>
+        <v>-4.06482528327474</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>216.0753098081747</v>
+        <v>331.0753098081667</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>23.1</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>39.72859468611846</v>
+        <v>39.72859471084847</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.98798827280412</v>
+        <v>16.98798830766939</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.5820629980034568</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1006356537381864</v>
+        <v>-0.1006356537622206</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6228</v>
+        <v>6462</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>203.1260083368414</v>
+        <v>320.7960989523402</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>17.9</v>
+        <v>94.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>53.46542245305526</v>
+        <v>37.7085107107297</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.91986399723198</v>
+        <v>17.89823966715626</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4379537396589566</v>
+        <v>0.9575104814134476</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.3623017908517514</v>
+        <v>-0.8839040516447449</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6474</v>
+        <v>6210</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>200.7527332458851</v>
+        <v>310.1014210435184</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>35.25</v>
+        <v>18.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.69531358061815</v>
+        <v>52.80685541865308</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.97232321744505</v>
+        <v>5.694140828737645</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5394357523450818</v>
+        <v>0.6835491309931969</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,11 +5711,11 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0609257640870128</v>
+        <v>0.0422826753727926</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>185.8696338239032</v>
+        <v>300.8696338239031</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>56.9</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>22.50627152678848</v>
+        <v>22.50627182473088</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.12847240540204</v>
+        <v>14.12847238328662</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.8619440460902719</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.2440218591639726</v>
+        <v>-0.2440218591880038</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6246</v>
+        <v>6235</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>182.3142156577222</v>
+        <v>297.8909384237587</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>12.5</v>
+        <v>35.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.34718260825923</v>
+        <v>35.64554402554077</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.82690775372742</v>
+        <v>18.01551880401261</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6231294131608616</v>
+        <v>0.9164846115325184</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,11 +5817,11 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0191272102593244</v>
+        <v>-0.25138394439228</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>182.1367288234141</v>
+        <v>297.136728823414</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>19.2</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.23716337646254</v>
+        <v>40.23716280402687</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>26.11785233560935</v>
+        <v>26.11785231893958</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.7938172672565651</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0209841994208562</v>
+        <v>-0.020984199348755</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6176</v>
+        <v>6208</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>160.5661711703858</v>
+        <v>295.7803342325957</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>91.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>51.6346579141676</v>
+        <v>35.67991471014378</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.451097327402865</v>
+        <v>16.55335724805238</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.136473076998046</v>
+        <v>0.6736731365557146</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.07942985208889471</v>
+        <v>-0.4409953358602952</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6235</v>
+        <v>6441</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>157.8909384237621</v>
+        <v>295.3421421364542</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>35.5</v>
+        <v>21.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>35.64554399523441</v>
+        <v>40.70890483760497</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.01551882949211</v>
+        <v>14.03806694874175</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.9164846115325184</v>
+        <v>0.2484632406903737</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.251383944584562</v>
+        <v>-0.3454738591193971</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6441</v>
+        <v>6220</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>155.3421421364542</v>
+        <v>292.8819604927273</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>21.5</v>
+        <v>25.05</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>40.70890484213</v>
+        <v>39.42486625760315</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.03806703349936</v>
+        <v>13.27729857532581</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.2484632406903737</v>
+        <v>0.4986649041908362</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.3454738591193971</v>
+        <v>0.0168245842561979</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6222</v>
+        <v>6261</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>155.0500729040144</v>
+        <v>289.6857104451202</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>19.25</v>
+        <v>76.3</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>50.84758835978341</v>
+        <v>42.90319674463365</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>7.152017298758458</v>
+        <v>13.6996117282331</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.496218109125451</v>
+        <v>0.6685710445120212</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.2146631730558872</v>
+        <v>-0.1145481954758806</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6243</v>
+        <v>6417</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>154.4284947469955</v>
+        <v>282.5603130601102</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>36.65</v>
+        <v>99.8</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>41.242493939171</v>
+        <v>37.86866144544849</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.87274733914203</v>
+        <v>25.74744843335915</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3751856836548015</v>
+        <v>1.490486142794386</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.140907141014443</v>
+        <v>0.0826093787235907</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6220</v>
+        <v>6442</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>152.8819604927273</v>
+        <v>280.0983996787767</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25.05</v>
+        <v>1495</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.42486623095591</v>
+        <v>42.77247828339761</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.27729855742876</v>
+        <v>18.76596318789625</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4986649041908362</v>
+        <v>0.5592058251376641</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0168245842561979</v>
+        <v>-16.5502556131711</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6405</v>
+        <v>6412</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>117.4909054213356</v>
+        <v>275.9788082511744</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>39.4</v>
+        <v>74.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,49 +6223,49 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45.56644341330463</v>
+        <v>49.41743827193144</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.16778348549119</v>
+        <v>16.39099902309644</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4105056283617592</v>
+        <v>0.8425469881425824</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.3652615655661527</v>
+        <v>0.2664022006481574</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6272</v>
+        <v>6222</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>108.7165269531992</v>
+        <v>270.0500729040141</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>23.4</v>
+        <v>19.25</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>37.16280504207142</v>
+        <v>50.84758836826762</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.60909058665091</v>
+        <v>7.152017296241132</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9651706368682282</v>
+        <v>0.496218109125451</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.1993218201378445</v>
+        <v>0.2146631730078187</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6412</v>
+        <v>6243</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>105.9788082511743</v>
+        <v>269.4284947469955</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>74.8</v>
+        <v>36.65</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>49.41743827193144</v>
+        <v>41.242493882943</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.39099900540144</v>
+        <v>15.87274735859336</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8425469881425824</v>
+        <v>0.3751856836548015</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,11 +6347,11 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.2664022006481574</v>
+        <v>-0.1409071407740931</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>96.87800497394016</v>
+        <v>236.8780049739402</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>39.8</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>37.91892849810927</v>
+        <v>37.91892863530592</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.7224179290282</v>
+        <v>19.72241786984066</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.5297084276611655</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0235834754962643</v>
+        <v>0.0235834754001241</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6237</v>
+        <v>6405</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>88.91764844738077</v>
+        <v>232.4909054213356</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>32.3</v>
+        <v>39.4</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,49 +6435,49 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>36.91674491075084</v>
+        <v>45.56644351195572</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.74847576035641</v>
+        <v>13.16778346041666</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3775327489455896</v>
+        <v>0.4105056283617592</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.3622695092032992</v>
+        <v>-0.365261565445981</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6276</v>
+        <v>6272</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>79.01623844917034</v>
+        <v>223.7165269531993</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>17.85</v>
+        <v>23.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.3002293077398</v>
+        <v>37.1628052668483</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>10.91390854573423</v>
+        <v>17.60909062914387</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1995475404317672</v>
+        <v>0.9651706368682282</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1455926995224463</v>
+        <v>-0.1993218200657426</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6283</v>
+        <v>6237</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>65.96892015243283</v>
+        <v>203.9176484473811</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>18.75</v>
+        <v>32.3</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.01576366810661</v>
+        <v>36.91674509371466</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.8929809008782</v>
+        <v>18.74847578724855</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.939058580070497</v>
+        <v>0.3775327489455896</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,9 +6559,62 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.036216473699065</v>
+        <v>-0.3622695091311964</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6276</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>安鈦克</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>79.01623844917047</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>48.30022933605838</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>10.91390836489169</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.1995475404317672</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.1455926991859636</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
